--- a/output/pdf_financials_xlsx/KLS.xlsx
+++ b/output/pdf_financials_xlsx/KLS.xlsx
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.634933</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.34774</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.405523</v>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.021339</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.490526</v>
       </c>
       <c r="K92" s="1" t="inlineStr">
         <is>
@@ -13620,7 +13620,11 @@
           <t>Reserves (Note 9 (b))</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -16944,7 +16948,11 @@
           <t>Share-based payments reserve (Note 10 (b)) 1,573,179</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18064,7 +18072,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KLS.xlsx
+++ b/output/pdf_financials_xlsx/KLS.xlsx
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.030809</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.028755</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003875</v>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.406738</v>
+        <v>-1.437547</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.454778</v>
+        <v>-3.483533</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-5.166207</v>
+        <v>-5.170082</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.406738</v>
+        <v>-1.437547</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.454778</v>
+        <v>-3.483533</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.166207</v>
+        <v>-5.170082</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-7.439074163561715</v>
+        <v>-7.601997491079117</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-42.77227727675491</v>
+        <v>-43.12828186897273</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-85.21187811923841</v>
+        <v>-85.27579271416502</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.266472</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.457934</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002582</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.433838</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.153147</v>
       </c>
     </row>
     <row r="35">
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.266472</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.457934</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002582</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.433838</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.153147</v>
       </c>
     </row>
     <row r="37">
@@ -3272,13 +3272,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.283058</v>
+        <v>0.016586</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.503689</v>
+        <v>0.045755</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.085581</v>
+        <v>0.082999</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
